--- a/协作/27-归档快照与校验.xlsx
+++ b/协作/27-归档快照与校验.xlsx
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1090,6 +1090,20 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>本仓库实际：</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>快照-0001 的「提交号」填的是被归档的内容基线 8a5c71d；版本标签 tm-v3.4 打在 38e02f7（内容基线 + 本记录 + 证据-0007）。二者差异仅为快照记录本身，这是 zip 无法包含自身哈希的固有限制。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/协作/27-归档快照与校验.xlsx
+++ b/协作/27-归档快照与校验.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>协作/归档/dcg-tm-v3.4.zip</t>
+          <t>归档/dcg-tm-v3.4.zip</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>通过：解包后 197 份文件，与 git archive 清单一致；zip 完整性检查无坏块</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -590,12 +590,67 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>证据-0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>快照-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>tm-v3.5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3f1aef4</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>归档/dcg-tm-v3.5.zip</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>817dfd0a930a01476d9cfe6777264cea594d5e9dac1998f431f134cef841c198</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sha256sum 协作/归档/dcg-tm-v3.5.zip；python zipfile 解包比对文件数与 26-归档清单</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="I2:I121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,失败"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/27-归档快照与校验.xlsx
+++ b/协作/27-归档快照与校验.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,6 +645,61 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>证据-0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>快照-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:05:00 +08:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>tm-v3.5.1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0436ca2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>归档/dcg-tm-v3.5.1.zip</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2a23f7e6ab808abc0bf8231ba3dc5802a7b43654e9240c7c119b7dbd3fcaff80</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>179</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>sha256sum 协作/归档/dcg-tm-v3.5.1.zip；python zipfile 解包比对文件数 179 与非目录条目 192</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>guozhizhuang</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>证据-0013</t>
         </is>
       </c>
     </row>
